--- a/utils/monday_sprint_sprint_2024-35.xlsx
+++ b/utils/monday_sprint_sprint_2024-35.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="173">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>25214</t>
+    <t>6347636185</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>28/03/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>09/05/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>25743</t>
+    <t>6531009703</t>
   </si>
   <si>
     <t>Valorização e Movimentação dos Estoques de Produtos - Saldo Inicial</t>
@@ -114,10 +114,13 @@
     <t>26/04/2024</t>
   </si>
   <si>
+    <t>30/04/2024</t>
+  </si>
+  <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>25592</t>
+    <t>6446155086</t>
   </si>
   <si>
     <t>Alteração Dashboard CheckList 5S</t>
@@ -129,19 +132,22 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>25359</t>
+    <t>6350699142</t>
   </si>
   <si>
     <t>Cores Gestão à vista Rebarbação VI</t>
   </si>
   <si>
-    <t>25487</t>
+    <t>6446399715</t>
   </si>
   <si>
     <t>Sistema de cadastro de modelos - vida útil dos modelos</t>
   </si>
   <si>
-    <t>22418</t>
+    <t>29/04/2024</t>
+  </si>
+  <si>
+    <t>6459507887</t>
   </si>
   <si>
     <t>Melhorias Sistema de Apontamentos Moldagem ULE - Configuração botoeiras</t>
@@ -153,7 +159,7 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>25012</t>
+    <t>6269168579</t>
   </si>
   <si>
     <t>Compara Carteira de Pedidos + Faturamento</t>
@@ -162,7 +168,7 @@
     <t>15/03/2024</t>
   </si>
   <si>
-    <t>23460</t>
+    <t>5894539031</t>
   </si>
   <si>
     <t>Análise</t>
@@ -174,10 +180,13 @@
     <t>19/01/2024</t>
   </si>
   <si>
+    <t>12/05/2024</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
-    <t>24295</t>
+    <t>6549800394</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -186,13 +195,10 @@
     <t>Compra SPOT - Recebimento do processo</t>
   </si>
   <si>
-    <t>30/04/2024</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>24277</t>
+    <t>5990534390</t>
   </si>
   <si>
     <t>Alterações Sistema de Ensaios Destrutivos</t>
@@ -201,34 +207,46 @@
     <t>02/02/2024</t>
   </si>
   <si>
+    <t>05/05/2024</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>25352</t>
+    <t>6348115072</t>
   </si>
   <si>
     <t>MELHORIA VENCIMENTOS - SISTEMA DE INVOICES</t>
   </si>
   <si>
-    <t>25218</t>
+    <t>08/05/2024</t>
+  </si>
+  <si>
+    <t>6347626987</t>
   </si>
   <si>
     <t>ALTERAÇÃO FILTRO SISTEMA DE GESTÃO A VISTA</t>
   </si>
   <si>
-    <t>25085</t>
+    <t>6268824076</t>
   </si>
   <si>
     <t>Buscar impostos XML</t>
   </si>
   <si>
+    <t>6549807094</t>
+  </si>
+  <si>
     <t>Compra SPOT - Retorno do processo</t>
   </si>
   <si>
-    <t>24420</t>
+    <t>06/05/2024</t>
+  </si>
+  <si>
+    <t>6034748618</t>
   </si>
   <si>
     <t>SISTEMA DE INVOICE - ALTERAÇÃO CERTIFICADO PARA CERTIFICADO DE FUMIGAÇÃO</t>
@@ -237,19 +255,25 @@
     <t>09/02/2024</t>
   </si>
   <si>
-    <t>19181</t>
+    <t>07/05/2024</t>
+  </si>
+  <si>
+    <t>6455019066</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais - Gerar mais de 02 OTFs de serviço</t>
   </si>
   <si>
-    <t>25538</t>
+    <t>02/05/2024</t>
+  </si>
+  <si>
+    <t>6446311776</t>
   </si>
   <si>
     <t>Controle EPIS</t>
   </si>
   <si>
-    <t>24270</t>
+    <t>6363129578</t>
   </si>
   <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE  - JANELA DE PAGTO/CLIENTE</t>
@@ -258,13 +282,19 @@
     <t>01/04/2024</t>
   </si>
   <si>
+    <t>6363553837</t>
+  </si>
+  <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE  - Integração com Benner (Envio da OTF com provisão)</t>
   </si>
   <si>
+    <t>6363841433</t>
+  </si>
+  <si>
     <t>ALTERAÇÃO PARCELAS SISTEMA INVOICE  - Integração com Benner (Exclusão de Provisões faturadas)</t>
   </si>
   <si>
-    <t>24901</t>
+    <t>6467807052</t>
   </si>
   <si>
     <t>Sistema de Previsão de Vendas (Ofertas e Forecast)</t>
@@ -273,31 +303,34 @@
     <t>16/04/2024</t>
   </si>
   <si>
-    <t>23316</t>
+    <t>6467807265</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - Ajustagem da Usinagem</t>
   </si>
   <si>
-    <t>25711</t>
+    <t>13/05/2024</t>
+  </si>
+  <si>
+    <t>6531230129</t>
   </si>
   <si>
     <t>Melhoria no portal de pendências</t>
   </si>
   <si>
-    <t>25710</t>
+    <t>6531240089</t>
   </si>
   <si>
     <t>Melhoria no portal de compras</t>
   </si>
   <si>
-    <t>25734</t>
+    <t>6531216148</t>
   </si>
   <si>
     <t>Melhorias Sistema de Custeio - Custo MP e MA</t>
   </si>
   <si>
-    <t>25640</t>
+    <t>6475336095</t>
   </si>
   <si>
     <t>Correção</t>
@@ -309,76 +342,82 @@
     <t>17/04/2024</t>
   </si>
   <si>
-    <t>25685</t>
+    <t>6532479712</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO FLUXO 105</t>
   </si>
   <si>
-    <t>25683</t>
+    <t>6532492565</t>
   </si>
   <si>
     <t>Apontamento de Retrabalho</t>
   </si>
   <si>
-    <t>25655</t>
+    <t>6532632549</t>
   </si>
   <si>
     <t>Notificação de devolução de Cliente</t>
   </si>
   <si>
-    <t>25612</t>
+    <t>6532679533</t>
   </si>
   <si>
     <t>FLUXO 106 E 107</t>
   </si>
   <si>
-    <t>25791</t>
+    <t>6533181742</t>
   </si>
   <si>
     <t>Planilha MPS USE - 84E902436ABG1</t>
   </si>
   <si>
-    <t>25765</t>
+    <t>6530844639</t>
   </si>
   <si>
     <t>[SUPRIMENTOS] Inclusão de informação no relatório de Entrada</t>
   </si>
   <si>
-    <t>25759</t>
+    <t>6530889257</t>
   </si>
   <si>
     <t>Dashboard desmoldagem</t>
   </si>
   <si>
-    <t>25787</t>
+    <t>6530721153</t>
   </si>
   <si>
     <t>Apontamentos de peça</t>
   </si>
   <si>
-    <t>25744</t>
+    <t>6530940702</t>
   </si>
   <si>
     <t>Bloqueio de requisição (óculos usinagem)</t>
   </si>
   <si>
-    <t>25736</t>
+    <t>6531205505</t>
   </si>
   <si>
     <t>Pré-lista de materiais</t>
   </si>
   <si>
-    <t>25668</t>
+    <t>6532615240</t>
   </si>
   <si>
     <t>Alteração maquinas pneumáticas</t>
   </si>
   <si>
+    <t>6549711182</t>
+  </si>
+  <si>
     <t>Cadastro de item - Compra spot</t>
   </si>
   <si>
-    <t>25875</t>
+    <t>04/05/2024</t>
+  </si>
+  <si>
+    <t>6577405681</t>
   </si>
   <si>
     <t>REQUISITOS PARA REBARBAÇÃO AUTOMATIZADA</t>
@@ -390,13 +429,10 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>25890</t>
-  </si>
-  <si>
-    <t>06/05/2024</t>
-  </si>
-  <si>
-    <t>24841</t>
+    <t>6586760155</t>
+  </si>
+  <si>
+    <t>6467917496</t>
   </si>
   <si>
     <t>Aplicação de Estoque Total</t>
@@ -408,7 +444,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-35</t>
+    <t>Jan/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1056,7 +1092,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1068,12 +1104,12 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1085,10 +1121,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1100,7 +1136,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -1112,15 +1148,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1132,10 +1168,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1167,7 +1203,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1179,10 +1215,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1194,10 +1230,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1206,15 +1242,15 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1226,10 +1262,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1241,7 +1277,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
@@ -1253,15 +1289,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1273,10 +1309,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1288,10 +1324,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1300,7 +1336,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1308,22 +1344,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1335,10 +1371,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1347,30 +1383,30 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1382,10 +1418,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1394,15 +1430,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1414,10 +1450,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1429,10 +1465,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1441,15 +1477,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1461,10 +1497,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1479,7 +1515,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1496,7 +1532,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1508,10 +1544,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1526,7 +1562,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1543,7 +1579,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1555,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1570,10 +1606,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1582,7 +1618,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1590,22 +1626,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1617,10 +1653,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1629,15 +1665,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1649,10 +1685,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -1664,10 +1700,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1676,30 +1712,30 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1711,10 +1747,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1723,15 +1759,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1743,10 +1779,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1758,10 +1794,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1770,15 +1806,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1790,10 +1826,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1805,10 +1841,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1817,15 +1853,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1837,10 +1873,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1852,10 +1888,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1864,15 +1900,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1884,10 +1920,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1899,10 +1935,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1911,15 +1947,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1931,10 +1967,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1946,10 +1982,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1958,15 +1994,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1978,10 +2014,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -1993,10 +2029,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2005,15 +2041,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2025,10 +2061,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -2043,7 +2079,7 @@
         <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2055,12 +2091,12 @@
         <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2072,10 +2108,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2090,7 +2126,7 @@
         <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2102,12 +2138,12 @@
         <v>27</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2119,10 +2155,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2137,7 +2173,7 @@
         <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2149,27 +2185,27 @@
         <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2181,10 +2217,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2193,15 +2229,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2213,10 +2249,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2231,7 +2267,7 @@
         <v>32</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2243,12 +2279,12 @@
         <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2260,10 +2296,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
@@ -2278,7 +2314,7 @@
         <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2290,12 +2326,12 @@
         <v>27</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2307,10 +2343,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2325,7 +2361,7 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2337,12 +2373,12 @@
         <v>27</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2354,10 +2390,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2372,7 +2408,7 @@
         <v>32</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2384,12 +2420,12 @@
         <v>27</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2401,10 +2437,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2419,7 +2455,7 @@
         <v>32</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2431,12 +2467,12 @@
         <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2448,10 +2484,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -2478,12 +2514,12 @@
         <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2495,10 +2531,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -2513,7 +2549,7 @@
         <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2525,27 +2561,27 @@
         <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
@@ -2560,7 +2596,7 @@
         <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2572,12 +2608,12 @@
         <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2589,10 +2625,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
@@ -2619,12 +2655,12 @@
         <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2636,10 +2672,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -2654,7 +2690,7 @@
         <v>32</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2666,12 +2702,12 @@
         <v>27</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2683,10 +2719,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
@@ -2701,7 +2737,7 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2713,12 +2749,12 @@
         <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2730,10 +2766,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
@@ -2745,10 +2781,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2757,15 +2793,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2777,10 +2813,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
@@ -2792,10 +2828,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2804,30 +2840,30 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -2839,10 +2875,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2851,15 +2887,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2871,10 +2907,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
@@ -2886,7 +2922,7 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>24</v>
@@ -2898,10 +2934,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2917,23 +2953,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2941,16 +2977,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2961,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>26.24</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2969,7 +3005,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2982,7 +3018,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2990,7 +3026,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3021,12 +3057,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>41</v>
@@ -3040,7 +3076,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3050,25 +3086,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3085,13 +3121,13 @@
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3103,15 +3139,15 @@
         <v>41</v>
       </c>
       <c r="P10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3129,21 +3165,21 @@
         <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3155,73 +3191,61 @@
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3229,7 +3253,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3237,7 +3261,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3245,10 +3269,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3256,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3264,142 +3288,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
